--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E1FE9F-3F9C-49F4-9110-47F8D26B3FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E3D6EE-623B-4CFF-B918-3C86AF698166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,10 @@
     <sheet name="CustomList" sheetId="3" r:id="rId2"/>
     <sheet name="CustomList2" sheetId="4" r:id="rId3"/>
     <sheet name="CustomData" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId7"/>
+    <sheet name="LOOKUPfunctions" sheetId="10" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Orders">DMart_Sales_Data[OrderID]</definedName>
@@ -37,14 +38,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3746" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3769" uniqueCount="689">
   <si>
     <t>Region</t>
   </si>
@@ -2153,6 +2154,15 @@
   <si>
     <t>Data</t>
   </si>
+  <si>
+    <t>EmployeeID</t>
+  </si>
+  <si>
+    <t>Using Vlookup&amp;Match</t>
+  </si>
+  <si>
+    <t>Using Index-Match</t>
+  </si>
 </sst>
 </file>
 
@@ -2162,11 +2172,18 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2329,7 +2346,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2428,6 +2445,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2797,77 +2820,77 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -2876,63 +2899,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="22" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
@@ -2943,20 +2966,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="40% - Accent3" xfId="3" builtinId="39"/>
@@ -3498,9 +3529,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE97132"/>
       <color rgb="FF66CCFF"/>
       <color rgb="FFCC0000"/>
-      <color rgb="FFE97132"/>
       <color rgb="FFFFCCFF"/>
       <color rgb="FFFF99FF"/>
     </mruColors>
@@ -5944,7 +5975,7 @@
         <v>No</v>
       </c>
       <c r="Q33" s="1"/>
-      <c r="R33" s="93" t="s">
+      <c r="R33" s="86" t="s">
         <v>674</v>
       </c>
       <c r="S33" s="86">
@@ -6013,7 +6044,7 @@
         <v>No</v>
       </c>
       <c r="Q34" s="1"/>
-      <c r="R34" s="93" t="s">
+      <c r="R34" s="86" t="s">
         <v>675</v>
       </c>
       <c r="S34" s="86">
@@ -6082,7 +6113,7 @@
         <v>No</v>
       </c>
       <c r="Q35" s="1"/>
-      <c r="R35" s="93" t="s">
+      <c r="R35" s="86" t="s">
         <v>676</v>
       </c>
       <c r="S35" s="86">
@@ -6151,7 +6182,7 @@
         <v>No</v>
       </c>
       <c r="Q36" s="1"/>
-      <c r="R36" s="93" t="s">
+      <c r="R36" s="86" t="s">
         <v>677</v>
       </c>
       <c r="S36" s="86">
@@ -6284,7 +6315,7 @@
         <v>No</v>
       </c>
       <c r="Q38" s="1"/>
-      <c r="R38" s="93" t="s">
+      <c r="R38" s="86" t="s">
         <v>678</v>
       </c>
       <c r="S38" s="86">
@@ -6353,7 +6384,7 @@
         <v>No</v>
       </c>
       <c r="Q39" s="1"/>
-      <c r="R39" s="93" t="s">
+      <c r="R39" s="86" t="s">
         <v>679</v>
       </c>
       <c r="S39" s="86">
@@ -6422,7 +6453,7 @@
         <v>No</v>
       </c>
       <c r="Q40" s="1"/>
-      <c r="R40" s="93" t="s">
+      <c r="R40" s="86" t="s">
         <v>680</v>
       </c>
       <c r="S40" s="86">
@@ -6491,7 +6522,7 @@
         <v>Yes</v>
       </c>
       <c r="Q41" s="1"/>
-      <c r="R41" s="93" t="s">
+      <c r="R41" s="86" t="s">
         <v>681</v>
       </c>
       <c r="S41" s="86">
@@ -6624,7 +6655,7 @@
         <v>Yes</v>
       </c>
       <c r="Q43" s="1"/>
-      <c r="R43" s="93" t="s">
+      <c r="R43" s="86" t="s">
         <v>682</v>
       </c>
       <c r="S43" s="86">
@@ -6693,7 +6724,7 @@
         <v>No</v>
       </c>
       <c r="Q44" s="1"/>
-      <c r="R44" s="93" t="s">
+      <c r="R44" s="86" t="s">
         <v>683</v>
       </c>
       <c r="S44" s="86">
@@ -6826,10 +6857,10 @@
         <v>No</v>
       </c>
       <c r="Q46" s="1"/>
-      <c r="R46" s="92" t="s">
+      <c r="R46" s="86" t="s">
         <v>684</v>
       </c>
-      <c r="S46" s="1">
+      <c r="S46" s="86">
         <f>SUMIF(I:I,"&gt;2024-06-30",E:E)</f>
         <v>368049.34999999992</v>
       </c>
@@ -49362,7 +49393,7 @@
       <c r="Y1000" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="E1:F1048576">
     <cfRule type="top10" dxfId="3" priority="2" bottom="1" rank="10"/>
     <cfRule type="top10" dxfId="2" priority="3" rank="10"/>
@@ -49543,7 +49574,7 @@
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="95" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="93" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>581</v>
       </c>
@@ -49552,10 +49583,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="92" t="s">
         <v>580</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="92" t="s">
         <v>583</v>
       </c>
     </row>
@@ -49851,7 +49882,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -50891,7 +50922,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D3:E14">
     <sortCondition ref="D3:D14" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E3:E14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>50000</formula>
@@ -50902,71 +50933,377 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA8BAB1-040E-441D-9B11-9B0DBA9BE36E}">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="97" t="s">
+        <v>686</v>
+      </c>
+      <c r="B1" s="95" t="s">
+        <v>608</v>
+      </c>
+      <c r="C1" s="95" t="s">
+        <v>577</v>
+      </c>
+      <c r="D1" s="95" t="s">
+        <v>638</v>
+      </c>
+      <c r="E1" s="95" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="27">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>583</v>
+      </c>
+      <c r="C2" s="27">
+        <v>70000</v>
+      </c>
+      <c r="D2" s="96">
+        <f>IF(C2&gt;=75000,15%,IF(C2&gt;=70000,10%,IF(C2&gt;=50000,5%,IF(C2&lt;50000,0))))</f>
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="27">
+        <f>C2*D2</f>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="27">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>587</v>
+      </c>
+      <c r="C3" s="27">
+        <v>50000</v>
+      </c>
+      <c r="D3" s="96">
+        <f t="shared" ref="D3:D9" si="0">IF(C3&gt;=75000,15%,IF(C3&gt;=70000,10%,IF(C3&gt;=50000,5%,IF(C3&lt;50000,0))))</f>
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="27">
+        <f t="shared" ref="E3:E9" si="1">C3*D3</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="27">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>584</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45000</v>
+      </c>
+      <c r="D4" s="96">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="27">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>585</v>
+      </c>
+      <c r="C5" s="27">
+        <v>75000</v>
+      </c>
+      <c r="D5" s="96">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="E5" s="27">
+        <f t="shared" si="1"/>
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="27">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>586</v>
+      </c>
+      <c r="C6" s="27">
+        <v>55000</v>
+      </c>
+      <c r="D6" s="96">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="E6" s="27">
+        <f t="shared" si="1"/>
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>588</v>
+      </c>
+      <c r="C7" s="27">
+        <v>48000</v>
+      </c>
+      <c r="D7" s="96">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="27">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>589</v>
+      </c>
+      <c r="C8" s="27">
+        <v>80000</v>
+      </c>
+      <c r="D8" s="96">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="27">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>590</v>
+      </c>
+      <c r="C9" s="27">
+        <v>40000</v>
+      </c>
+      <c r="D9" s="96">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="99" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="98" t="s">
+        <v>686</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>577</v>
+      </c>
+      <c r="E12" s="100" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="27">
+        <v>1001</v>
+      </c>
+      <c r="D13" s="27">
+        <f>VLOOKUP(C13,$A$1:$E$9,MATCH("Sales",$A$1:$E$1,0),FALSE)</f>
+        <v>70000</v>
+      </c>
+      <c r="E13" s="27">
+        <f>VLOOKUP(C13,A2:E9,MATCH(E1,A1:E1,0),FALSE)</f>
+        <v>7000</v>
+      </c>
+      <c r="H13" s="101">
+        <f>MATCH("Sales",A1:E1,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="27">
+        <v>1002</v>
+      </c>
+      <c r="D14" s="27">
+        <f>VLOOKUP(C14,$A$1:$E$9,MATCH("Sales",$A$1:$E$1,0),FALSE)</f>
+        <v>50000</v>
+      </c>
+      <c r="E14" s="27">
+        <f>VLOOKUP(C14,A3:E10,MATCH(E2,A2:E2,0),FALSE)</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="27">
+        <v>1003</v>
+      </c>
+      <c r="D15" s="27">
+        <f>VLOOKUP(C15,$A$1:$E$9,MATCH("Sales",$A$1:$E$1,0),FALSE)</f>
+        <v>45000</v>
+      </c>
+      <c r="E15" s="27">
+        <f>VLOOKUP(C15,A4:E11,MATCH(E3,A3:E3,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="99" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="102" t="s">
+        <v>686</v>
+      </c>
+      <c r="D18" s="102" t="s">
+        <v>577</v>
+      </c>
+      <c r="E18" s="103" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="27">
+        <v>1003</v>
+      </c>
+      <c r="D19" s="27">
+        <f>INDEX(A2:E9,3,3)</f>
+        <v>45000</v>
+      </c>
+      <c r="E19" s="27">
+        <f>INDEX($A$2:$E$9,MATCH(C19,$A$2:$A$9,0),MATCH($E$1,$A$1:$E$1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="27">
+        <v>1004</v>
+      </c>
+      <c r="D20" s="27">
+        <f t="shared" ref="D20:D21" si="2">INDEX(A3:E10,3,3)</f>
+        <v>75000</v>
+      </c>
+      <c r="E20" s="27">
+        <f t="shared" ref="E20:E21" si="3">INDEX($A$2:$E$9,MATCH(C20,$A$2:$A$9,0),MATCH($E$1,$A$1:$E$1,0))</f>
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="27">
+        <v>1005</v>
+      </c>
+      <c r="D21" s="27">
+        <f t="shared" si="2"/>
+        <v>55000</v>
+      </c>
+      <c r="E21" s="27">
+        <f t="shared" si="3"/>
+        <v>2750</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13:C15 C19" xr:uid="{EA1DFDD7-EA19-432F-9135-1EEE37691A5F}">
+      <formula1>$A$2:$A$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE4AEB2-99B1-4F87-956C-8EC68CB27B81}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="96" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="94" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="95">
+      <c r="A2" s="93">
         <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="95">
+      <c r="A3" s="93">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="95">
+      <c r="A4" s="93">
         <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="95">
+      <c r="A5" s="93">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="95">
+      <c r="A6" s="93">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="95">
+      <c r="A7" s="93">
         <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="95"/>
+      <c r="A8" s="93"/>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="95"/>
+      <c r="A9" s="93"/>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="95"/>
+      <c r="A10" s="93"/>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="95"/>
+      <c r="A11" s="93"/>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95"/>
+      <c r="A12" s="93"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A885D05-95FE-496B-A37F-A62FFC99FFE7}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51035,12 +51372,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F9E0CCF-A626-41AD-8D97-0A4946B1AEFD}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51109,7 +51446,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E3D6EE-623B-4CFF-B918-3C86AF698166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3DA336-070A-4D7E-A59B-07EEF0191C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DMart_Data_Set" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="CustomList2" sheetId="4" r:id="rId3"/>
     <sheet name="CustomData" sheetId="5" r:id="rId4"/>
     <sheet name="LOOKUPfunctions" sheetId="10" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
+    <sheet name="HLOOKUP" sheetId="11" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="Orders">DMart_Sales_Data[OrderID]</definedName>
@@ -38,14 +39,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3769" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="698">
   <si>
     <t>Region</t>
   </si>
@@ -2163,6 +2164,33 @@
   <si>
     <t>Using Index-Match</t>
   </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Using VLOOKUP</t>
+  </si>
 </sst>
 </file>
 
@@ -2172,11 +2200,18 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2820,77 +2855,77 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -2899,63 +2934,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="22" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="23" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
@@ -2966,28 +3001,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="40% - Accent3" xfId="3" builtinId="39"/>
@@ -49393,7 +49430,7 @@
       <c r="Y1000" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="E1:F1048576">
     <cfRule type="top10" dxfId="3" priority="2" bottom="1" rank="10"/>
     <cfRule type="top10" dxfId="2" priority="3" rank="10"/>
@@ -49882,7 +49919,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -50922,7 +50959,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D3:E14">
     <sortCondition ref="D3:D14" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="E3:E14">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>50000</formula>
@@ -51228,7 +51265,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13:C15 C19" xr:uid="{EA1DFDD7-EA19-432F-9135-1EEE37691A5F}">
       <formula1>$A$2:$A$9</formula1>
@@ -51239,6 +51276,198 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FABEF5C-D0AD-491C-B800-CFAE06B8007C}">
+  <dimension ref="A2:F14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>692</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>693</v>
+      </c>
+      <c r="B3" s="27">
+        <v>100</v>
+      </c>
+      <c r="C3" s="27">
+        <v>585</v>
+      </c>
+      <c r="D3" s="27">
+        <v>333</v>
+      </c>
+      <c r="E3" s="27">
+        <v>745</v>
+      </c>
+      <c r="F3" s="27">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>694</v>
+      </c>
+      <c r="B4" s="27">
+        <v>100</v>
+      </c>
+      <c r="C4" s="27">
+        <v>500</v>
+      </c>
+      <c r="D4" s="27">
+        <v>600</v>
+      </c>
+      <c r="E4" s="27">
+        <v>700</v>
+      </c>
+      <c r="F4" s="27">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="B5" s="27">
+        <v>2000</v>
+      </c>
+      <c r="C5" s="27">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="27">
+        <v>8000</v>
+      </c>
+      <c r="E5" s="27">
+        <v>6000</v>
+      </c>
+      <c r="F5" s="27">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>695</v>
+      </c>
+      <c r="B6" s="27">
+        <v>400</v>
+      </c>
+      <c r="C6" s="27">
+        <v>500</v>
+      </c>
+      <c r="D6" s="27">
+        <v>300</v>
+      </c>
+      <c r="E6" s="27">
+        <v>300</v>
+      </c>
+      <c r="F6" s="27">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E9" s="105" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="25" t="s">
+        <v>696</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>692</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>696</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="C11" s="27">
+        <f>HLOOKUP($C$10,$A$2:$F$6,MATCH(B11,$A$2:$A$6,0),FALSE)</f>
+        <v>6000</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="F11" s="27">
+        <f>VLOOKUP(E11,$A$2:$F$6,MATCH($F$10,$A$2:$F$2,0),FALSE)</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="25" t="s">
+        <v>694</v>
+      </c>
+      <c r="C12" s="27">
+        <f>HLOOKUP($C$10,$A$2:$F$6,MATCH(B12,$A$2:$A$6,0),FALSE)</f>
+        <v>700</v>
+      </c>
+      <c r="E12" s="104" t="s">
+        <v>695</v>
+      </c>
+      <c r="F12" s="27">
+        <f t="shared" ref="F12:F14" si="0">VLOOKUP(E12,$A$2:$F$6,MATCH($F$10,$A$2:$F$2,0),FALSE)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="104" t="s">
+        <v>693</v>
+      </c>
+      <c r="C13" s="27">
+        <f>HLOOKUP($C$10,$A$2:$F$6,MATCH(B13,$A$2:$A$6,0),FALSE)</f>
+        <v>745</v>
+      </c>
+      <c r="E13" s="104" t="s">
+        <v>693</v>
+      </c>
+      <c r="F13" s="27">
+        <f t="shared" si="0"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="104" t="s">
+        <v>695</v>
+      </c>
+      <c r="C14" s="27">
+        <f>HLOOKUP($C$10,$A$2:$F$6,MATCH(B14,$A$2:$A$6,0),FALSE)</f>
+        <v>300</v>
+      </c>
+      <c r="E14" s="104" t="s">
+        <v>694</v>
+      </c>
+      <c r="F14" s="27">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE4AEB2-99B1-4F87-956C-8EC68CB27B81}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51297,13 +51526,13 @@
       <c r="A12" s="93"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A885D05-95FE-496B-A37F-A62FFC99FFE7}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51372,12 +51601,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F9E0CCF-A626-41AD-8D97-0A4946B1AEFD}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51446,7 +51675,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\AdvExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03E3F6F-9489-48B0-8C22-882949379580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91ABD5A-FCDC-47E0-91DB-4A21E27D6767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2898,7 +2898,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3062,9 +3062,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="14" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3075,8 +3073,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="40% - Accent3" xfId="3" builtinId="39"/>
@@ -3868,25 +3864,25 @@
   <dimension ref="A1:AA1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" customWidth="1"/>
-    <col min="16" max="16" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" customWidth="1"/>
+    <col min="16" max="16" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.5703125" customWidth="1"/>
     <col min="18" max="18" width="63.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="25" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7079,10 +7075,10 @@
         <v>Yes</v>
       </c>
       <c r="Q48" s="1"/>
-      <c r="R48" s="113" t="s">
+      <c r="R48" s="111" t="s">
         <v>662</v>
       </c>
-      <c r="S48" s="113" t="s">
+      <c r="S48" s="111" t="s">
         <v>576</v>
       </c>
       <c r="T48" s="1"/>
@@ -7147,10 +7143,10 @@
         <v>No</v>
       </c>
       <c r="Q49" s="1"/>
-      <c r="R49" s="114" t="s">
+      <c r="R49" s="90" t="s">
         <v>475</v>
       </c>
-      <c r="S49" s="115">
+      <c r="S49" s="86">
         <f>VLOOKUP(R49,DMart_Sales_Data[#All],MATCH(DMart_Sales_Data[[#Headers],[Sales]],DMart_Sales_Data[#Headers],0),FALSE)</f>
         <v>292.56</v>
       </c>
@@ -51421,8 +51417,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="105"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="27"/>
@@ -51441,8 +51437,8 @@
       <c r="F2" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="AA2" s="106"/>
-      <c r="AB2" s="106"/>
+      <c r="AA2" s="105"/>
+      <c r="AB2" s="105"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
@@ -51463,8 +51459,8 @@
       <c r="F3" s="27">
         <v>222</v>
       </c>
-      <c r="AA3" s="106"/>
-      <c r="AB3" s="106"/>
+      <c r="AA3" s="105"/>
+      <c r="AB3" s="105"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
@@ -51485,8 +51481,8 @@
       <c r="F4" s="27">
         <v>900</v>
       </c>
-      <c r="AA4" s="106"/>
-      <c r="AB4" s="106"/>
+      <c r="AA4" s="105"/>
+      <c r="AB4" s="105"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
@@ -51507,8 +51503,8 @@
       <c r="F5" s="27">
         <v>4000</v>
       </c>
-      <c r="AA5" s="106"/>
-      <c r="AB5" s="106"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -51630,10 +51626,10 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.7109375" style="109" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="107" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="111" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="109" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>697</v>
       </c>
@@ -51641,7 +51637,7 @@
       <c r="C1" s="95" t="s">
         <v>698</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="108" t="s">
         <v>699</v>
       </c>
       <c r="E1" s="95" t="s">
@@ -51652,13 +51648,13 @@
       <c r="A2" s="27">
         <v>21</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="110" t="s">
         <v>700</v>
       </c>
       <c r="C2" s="27">
         <v>3</v>
       </c>
-      <c r="D2" s="108">
+      <c r="D2" s="106">
         <v>45854</v>
       </c>
       <c r="E2" s="27">
@@ -51669,19 +51665,19 @@
       <c r="A3" s="27">
         <v>18</v>
       </c>
-      <c r="B3" s="112" t="s">
+      <c r="B3" s="110" t="s">
         <v>701</v>
       </c>
       <c r="C3" s="27">
         <v>12</v>
       </c>
-      <c r="D3" s="108">
+      <c r="D3" s="106">
         <v>45855</v>
       </c>
       <c r="E3" s="27">
         <v>54</v>
       </c>
-      <c r="F3" s="107">
+      <c r="F3">
         <v>40</v>
       </c>
     </row>
@@ -51689,19 +51685,19 @@
       <c r="A4" s="27">
         <v>60</v>
       </c>
-      <c r="B4" s="112" t="s">
+      <c r="B4" s="110" t="s">
         <v>702</v>
       </c>
       <c r="C4" s="27">
         <v>2</v>
       </c>
-      <c r="D4" s="108">
+      <c r="D4" s="106">
         <v>45856</v>
       </c>
       <c r="E4" s="27">
         <v>69</v>
       </c>
-      <c r="F4" s="107">
+      <c r="F4">
         <v>75</v>
       </c>
     </row>
@@ -51709,129 +51705,129 @@
       <c r="A5" s="27">
         <v>21</v>
       </c>
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="110" t="s">
         <v>703</v>
       </c>
       <c r="C5" s="27">
         <v>10</v>
       </c>
-      <c r="D5" s="108">
+      <c r="D5" s="106">
         <v>45857</v>
       </c>
       <c r="E5" s="27"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="105">
+      <c r="A6" s="27">
         <v>56</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="110" t="s">
         <v>704</v>
       </c>
       <c r="C6" s="27"/>
-      <c r="D6" s="108">
+      <c r="D6" s="106">
         <v>45858</v>
       </c>
       <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="105">
+      <c r="A7" s="27">
         <v>34</v>
       </c>
-      <c r="B7" s="112" t="s">
+      <c r="B7" s="110" t="s">
         <v>705</v>
       </c>
       <c r="C7" s="27"/>
-      <c r="D7" s="108"/>
+      <c r="D7" s="106"/>
       <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="105">
+      <c r="A8" s="27">
         <v>14</v>
       </c>
-      <c r="B8" s="112"/>
+      <c r="B8" s="110"/>
       <c r="C8" s="27"/>
-      <c r="D8" s="108"/>
+      <c r="D8" s="106"/>
       <c r="E8" s="27"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="105">
+      <c r="A9" s="27">
         <v>55</v>
       </c>
-      <c r="B9" s="105"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="27"/>
-      <c r="D9" s="108"/>
+      <c r="D9" s="106"/>
       <c r="E9" s="27"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="105">
+      <c r="A10" s="27">
         <v>34</v>
       </c>
-      <c r="B10" s="105"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="27"/>
-      <c r="D10" s="108"/>
+      <c r="D10" s="106"/>
       <c r="E10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="105">
+      <c r="A11" s="27">
         <v>46</v>
       </c>
-      <c r="B11" s="105"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="27"/>
-      <c r="D11" s="108"/>
+      <c r="D11" s="106"/>
       <c r="E11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="105">
+      <c r="A12" s="27">
         <v>78</v>
       </c>
-      <c r="B12" s="105"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="27"/>
-      <c r="D12" s="108"/>
+      <c r="D12" s="106"/>
       <c r="E12" s="27"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="105">
+      <c r="A13" s="27">
         <v>19</v>
       </c>
-      <c r="B13" s="105"/>
+      <c r="B13" s="27"/>
       <c r="C13" s="27"/>
-      <c r="D13" s="108"/>
+      <c r="D13" s="106"/>
       <c r="E13" s="27"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="105">
+      <c r="A14" s="27">
         <v>23</v>
       </c>
-      <c r="B14" s="105"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="27"/>
-      <c r="D14" s="108"/>
+      <c r="D14" s="106"/>
       <c r="E14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="105">
+      <c r="A15" s="27">
         <v>53</v>
       </c>
-      <c r="B15" s="105"/>
+      <c r="B15" s="27"/>
       <c r="C15" s="27"/>
-      <c r="D15" s="108"/>
+      <c r="D15" s="106"/>
       <c r="E15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="105">
+      <c r="A16" s="27">
         <v>12</v>
       </c>
-      <c r="B16" s="105"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="27"/>
-      <c r="D16" s="108"/>
+      <c r="D16" s="106"/>
       <c r="E16" s="27"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="105">
+      <c r="A17" s="27">
         <v>20</v>
       </c>
-      <c r="B17" s="105"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="27"/>
-      <c r="D17" s="108"/>
+      <c r="D17" s="106"/>
       <c r="E17" s="27"/>
     </row>
   </sheetData>
